--- a/docs/pleth files meta data.xlsx
+++ b/docs/pleth files meta data.xlsx
@@ -270,10 +270,10 @@
     <t>Irregularity (frequency)</t>
   </si>
   <si>
-    <t>IBI irregularity - def 1</t>
+    <t>IBI irregularity - def 1 "CoV"</t>
   </si>
   <si>
-    <t>CoV of instantaneous breathing frequency or inter-breath interval</t>
+    <t>abs | ((Ti+Te) breath n - (Ti+Te) breath n+1) / (Ti+Te) breath n+1) |</t>
   </si>
   <si>
     <t>mean for each time periods; value over time across the ictal (1 second bin) and the postictal time period (30 second bin)</t>
@@ -283,10 +283,10 @@
 - to help us see where this comes from, generate histogram of ictal Ttot values for each trace</t>
   </si>
   <si>
-    <t>IBI irregularity - def 2</t>
+    <t>IBI irregularity - def 2 "Instantaneous"</t>
   </si>
   <si>
-    <t>abs | ((Ti+Te) breath n - (Ti+Te) breath n+1) / (Ti+Te) breath n+1) |</t>
+    <t>CoV of instantaneous breathing frequency or inter-breath interval</t>
   </si>
   <si>
     <t>Amplitudes</t>
